--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -390,7 +390,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -590,7 +590,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -619,7 +619,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -699,7 +699,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -989,7 +989,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1147,7 +1147,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1170,7 +1170,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1269,7 +1269,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1540,7 +1540,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1572,7 +1572,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1691,7 +1691,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1719,7 +1719,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1799,7 +1799,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1849,7 +1849,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1885,7 +1885,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1922,7 +1922,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1944,7 +1944,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -4476,7 +4476,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>198</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>221</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>236</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>250</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>268</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>304</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>353</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>380</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>429</v>
       </c>
@@ -10148,7 +10148,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>437</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>458</v>
       </c>
@@ -10512,7 +10512,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>466</v>
       </c>
@@ -10632,7 +10632,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>475</v>
       </c>
@@ -10754,7 +10754,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>483</v>
       </c>
@@ -13998,7 +13998,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>622</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
         <v>632</v>
       </c>
@@ -14602,7 +14602,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
         <v>638</v>
       </c>
@@ -14724,7 +14724,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>647</v>
       </c>
@@ -15092,12 +15092,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP105">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.5</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.61</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.61</t>
+    <t>0.9.71</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.71</t>
+    <t>0.9.72</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.72</t>
+    <t>0.9.73</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.73</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-heartrate.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
